--- a/templates/Experiments lrGS.xlsx
+++ b/templates/Experiments lrGS.xlsx
@@ -29,9 +29,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A reference to one or more individuals
-associated to the process
- Select one or more items from
+          <t>Select one or more items from
 Individuals</t>
         </r>
       </text>
@@ -45,10 +43,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>One or more characters used to identify,
-name, or characterize the nature,
-properties, or contents of a sample
- Select one item from Sample identifiers</t>
+          <t>Select one item from Sample identifiers</t>
         </r>
       </text>
     </comment>
@@ -61,10 +56,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>An identifier associated with a
-particular source, used by the data
-provider or owner
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -77,9 +69,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>One or more associations between the
-individual and an organisation.
- Select one or more items from
+          <t>Select one or more items from
 Organisations</t>
         </r>
       </text>
@@ -93,10 +83,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A data field which describes the name of
-the third party company or laboratory
-that provided services.
- Select one item from Organisations</t>
+          <t>Select one item from Organisations</t>
         </r>
       </text>
     </comment>
@@ -109,8 +96,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>E.g. genomic source
- Select one item from Library source</t>
+          <t>Select one item from Library source</t>
         </r>
       </text>
     </comment>
@@ -123,10 +109,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Method used to determine the order of
-bases in a nucleic acid sequence. In
-FAIR Genomes: SequencingMethod.
- Select one item from Sequencing methods</t>
+          <t>Select one item from Sequencing methods</t>
         </r>
       </text>
     </comment>
@@ -139,9 +122,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The vendor name for the nucleotide
-sequencing library preparation kit.
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -154,16 +135,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Pre-filled, ready-to-use reagent
-cartridges intented to improve
-chemistry, cluster density and read
-length as well as improve quality (Q)
-scores for this sample. Reagent
-components are encoded to interact with
-the sequencing system to validate
-compatibility with user-defined
-applications.
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -176,10 +148,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A machine-readable representation of an
-instrument (e.g., a sequencer) in a
-visual format on a surface
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -192,11 +161,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The name of the sequencing platform
-(i.e. brand, name of a company that
-produces sequencer equipment). In FAIR
-Genomes: SequencingPlatform.
- Select one item from Sequencing
+          <t>Select one item from Sequencing
 platforms</t>
         </r>
       </text>
@@ -210,11 +175,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The name of the product and model number
-of a manufacturer's genomic (dna)
-sequencer. In FAIR Genomes:
-SequencingInstrumentModel.
- Select one item from Sequencing
+          <t>Select one item from Sequencing
 instrument models</t>
         </r>
       </text>
@@ -228,11 +189,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A laboratory sequencing datum which
-describes the method and chemistry used
-to determine the order of nucleotides in
-a DNA molecule
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -245,8 +202,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>When the sequencing run took place
- DATETIME</t>
+          <t>DATETIME (yyyy-mm-dd hh:mm:ss)</t>
         </r>
       </text>
     </comment>
@@ -259,8 +215,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The number of samples per flow cell
- INTEGER</t>
+          <t>INTEGER</t>
         </r>
       </text>
     </comment>
@@ -273,11 +228,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A flow cell identifier is an identifier
-that identifies some flow cell (aparatus
-in the fluidic subsystem where the
-sheath and sample meet)
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -290,13 +241,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The unique number assigned to an
-instrument (e.g., a sequencer). This
-could either be the serial number, a
-unique ID generated by the data
-provider/owner, or another character
-string used to identify the instrument
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -309,9 +254,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The instrument (e.g., a sequencer)
-software
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -324,9 +267,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The source-specific version of the
-published genome assembly.
- Select one item from Genome accessions</t>
+          <t>Select one item from Genome accessions</t>
         </r>
       </text>
     </comment>
@@ -339,10 +280,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A sequence of characters used to
-uniquely identify a particular run of a
-test on a particular batch of samples
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -355,9 +293,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Output generated as biomass or product
-from a set of chemical reactions
- DECIMAL</t>
+          <t>DECIMAL</t>
         </r>
       </text>
     </comment>
@@ -370,10 +306,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The mean number of times a particular
-locus (site, nucleotide, amplicon,
-region) was sequenced.
- DECIMAL</t>
+          <t>DECIMAL</t>
         </r>
       </text>
     </comment>
@@ -386,10 +319,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The median number of times a particular
-locus (site, nucleotide, amplicon,
-region) was sequenced.
- DECIMAL</t>
+          <t>DECIMAL</t>
         </r>
       </text>
     </comment>
@@ -402,11 +332,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The mean number of nucleotides
-successfully ordered from each side of a
-nucleic acid fragment obtained after the
-completion of a sequencing process
- DECIMAL</t>
+          <t>DECIMAL</t>
         </r>
       </text>
     </comment>
@@ -419,20 +345,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The weighted median item size or N50 is
-a weighted median of the lengths of
-items, equal to the length of the
-longest item i such that the sum of the
-lengths of items greater than or equal
-in length to i is greater than or equal
-to half the length of all of the items.
-With regard to assemblies the items are
-typically contigs or scaffolds. It
-therefore denotes the ability of the
-software to create contigs and provides
-information about the resulting sequence
-assembly
- DECIMAL</t>
+          <t>DECIMAL</t>
         </r>
       </text>
     </comment>
@@ -445,10 +358,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Map rate (%) is the percentage of
-sequencing reads that successfully align
-to a reference genome.
- DECIMAL</t>
+          <t>DECIMAL</t>
         </r>
       </text>
     </comment>
@@ -461,9 +371,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>rate at which bases are produced or
-processed by the sequencing instrument
- DECIMAL</t>
+          <t>DECIMAL</t>
         </r>
       </text>
     </comment>
@@ -476,10 +384,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The percentage of sequenced bases whose
-Phred quality score exceeds 25,
-indicating high-confidence base calls
- DECIMAL</t>
+          <t>DECIMAL</t>
         </r>
       </text>
     </comment>
@@ -492,22 +397,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Other NGS quality control metrics,
-including but not limited to (i)
-sequencer metrics such as yield, error
-rate, density (K/mm2), cluster PF (%)
-and phas/prephas (%), (ii) alignment
-metrics such as QM insert size, GC
-content, QM duplicated reads (%), QM
-error rate, uniformity/evenness of
-coverage and maternal cell
-contamination, and (iii) variant call
-metrics such as number of SNVs/CNVs/SVs
-called, number of missense/nonsense
-variants, common variants (%), unique
-variants (%), gender match and trio
-inheritance check
- TEXT</t>
+          <t>TEXT</t>
         </r>
       </text>
     </comment>
@@ -520,11 +410,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Percentage of reads with a Phred quality
-score over 30, which indicates less than
-a 1/1000 chance that the base was called
-incorrectly.
- DECIMAL</t>
+          <t>DECIMAL</t>
         </r>
       </text>
     </comment>
@@ -537,10 +423,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The version of the software used to call
-the nucleotide bases in a sequencing
-assay
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -553,10 +436,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Analysis or reanalysis of existing data
-collected by another centre usually for
-a different purpose
- Select one or more items from
+          <t>Select one or more items from
 Organisations</t>
         </r>
       </text>
@@ -570,9 +450,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A datum which describes the version of
-the bioinformatics pipeline used.
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -585,9 +463,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A written explanation, observation or
-criticism added to textual material
- TEXT</t>
+          <t>TEXT</t>
         </r>
       </text>
     </comment>
